--- a/Simulation/Results/p.rand_Ten.Fixed.Ints_mean.surv.70.xlsx
+++ b/Simulation/Results/p.rand_Ten.Fixed.Ints_mean.surv.70.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">rand</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2 hours</t>
+    <t xml:space="preserve">5.7 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 hours</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0527</v>
+        <v>0.0502</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0549</v>
+        <v>0.0525</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0541</v>
+        <v>0.0495</v>
       </c>
       <c r="E2" t="n">
         <v>0.0142857142857143</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0523</v>
+        <v>0.0506</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0554</v>
+        <v>0.0533</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0523</v>
+        <v>0.051</v>
       </c>
       <c r="E3" t="n">
         <v>0.0142857142857143</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.047</v>
+        <v>0.0455</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0539</v>
+        <v>0.053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0555</v>
+        <v>0.055</v>
       </c>
       <c r="E4" t="n">
         <v>0.0142857142857143</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0456</v>
+        <v>0.047</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0532</v>
+        <v>0.0542</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0538</v>
+        <v>0.0542</v>
       </c>
       <c r="E5" t="n">
         <v>0.0142857142857143</v>
